--- a/fix-error-hapi-sp/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/fix-error-hapi-sp/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T14:52:58+00:00</t>
+    <t>2026-06-03T09:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-error-hapi-sp/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/fix-error-hapi-sp/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:54:44+00:00</t>
+    <t>2026-06-03T12:01:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
